--- a/semantic model development/score_analysis_project_QAxTactics/src/score_analysis_project/data/SMS + Multicase/data-quality-attributes.xlsx
+++ b/semantic model development/score_analysis_project_QAxTactics/src/score_analysis_project/data/SMS + Multicase/data-quality-attributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phili\Dropbox\01_Dev\02_QualiTact\Repository\QualiTact\semantic model development\score_analysis_project_QAxTactics\src\score_analysis_project\data\SMS + Multicase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66C1F96-1EDF-4439-B2FA-73F2FD695EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2D7233-6B58-45CD-8E6C-8503DD12B708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>User interface aesthetics</t>
   </si>
   <si>
-    <t>Accessability</t>
-  </si>
-  <si>
     <t>User controlability</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>Confidentiality</t>
   </si>
   <si>
-    <t xml:space="preserve">Integrity </t>
-  </si>
-  <si>
     <t>Non-repudiation</t>
   </si>
   <si>
@@ -148,12 +142,6 @@
   </si>
   <si>
     <t xml:space="preserve">Analysability </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modifiability </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testability </t>
   </si>
   <si>
     <t>Portability</t>
@@ -180,9 +168,6 @@
     <t>Interpretability</t>
   </si>
   <si>
-    <t xml:space="preserve">Verifiability </t>
-  </si>
-  <si>
     <t>Lightweight</t>
   </si>
   <si>
@@ -202,6 +187,21 @@
   </si>
   <si>
     <t>Physically small</t>
+  </si>
+  <si>
+    <t>Modifiability</t>
+  </si>
+  <si>
+    <t>Testability</t>
+  </si>
+  <si>
+    <t>Verifiability</t>
+  </si>
+  <si>
+    <t>Integrity</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
   </si>
 </sst>
 </file>
@@ -602,118 +602,118 @@
         <v>17</v>
       </c>
       <c r="S1" t="s">
+        <v>55</v>
+      </c>
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AO1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AP1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AQ1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AR1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AS1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AT1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AU1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AV1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AW1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BA1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BB1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BC1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BD1" t="s">
         <v>49</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.3">
